--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_With_Decisions.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_With_Decisions.xlsx
@@ -38,7 +38,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated April 29, 2026 · llc_single</t>
+    <t>Generated May 1, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -785,7 +785,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_With_Decisions.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_With_Decisions.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Decision History'!$A1:$H11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Decision History'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Financial Health'!$A1:$I40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -38,7 +38,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated May 1, 2026 · llc_single</t>
+    <t>Generated May 7, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -760,7 +760,7 @@
   </si>
   <si>
     <t xml:space="preserve">• Enrollment -8 cumulative
-• Tuition $-500/student</t>
+• Tuition -$500/student</t>
   </si>
   <si>
     <t>Board declined; enrollment goals retained as originally modeled.</t>
@@ -785,7 +785,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -920,7 +920,7 @@
     <t>The model reaches profit early and sustains strong margins through Year 5.</t>
   </si>
   <si>
-    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+    <t>Compare your real Year 1 enrollment against this projection as students enroll.</t>
   </si>
   <si>
     <t>Liquidity</t>
@@ -5901,7 +5901,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5911,7 +5911,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>247</v>
       </c>
@@ -5921,8 +5921,9 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="54" t="s">
         <v>248</v>
       </c>
@@ -5932,6 +5933,7 @@
       <c r="F3" s="54"/>
       <c r="G3" s="54"/>
       <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="55" t="s">
@@ -6422,7 +6424,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="12" t="s">
         <v>286</v>
       </c>
@@ -6438,8 +6440,9 @@
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="12"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="72" t="s">
         <v>290</v>
       </c>
@@ -6455,8 +6458,9 @@
       </c>
       <c r="G30" s="74"/>
       <c r="H30" s="74"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="74"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="72" t="s">
         <v>294</v>
       </c>
@@ -6472,8 +6476,9 @@
       </c>
       <c r="G31" s="74"/>
       <c r="H31" s="74"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="74"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="72" t="s">
         <v>297</v>
       </c>
@@ -6489,8 +6494,9 @@
       </c>
       <c r="G32" s="74"/>
       <c r="H32" s="74"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="74"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="72" t="s">
         <v>300</v>
       </c>
@@ -6506,8 +6512,9 @@
       </c>
       <c r="G33" s="74"/>
       <c r="H33" s="74"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="74"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="72" t="s">
         <v>303</v>
       </c>
@@ -6523,8 +6530,9 @@
       </c>
       <c r="G34" s="74"/>
       <c r="H34" s="74"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="74"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="72" t="s">
         <v>306</v>
       </c>
@@ -6540,8 +6548,9 @@
       </c>
       <c r="G35" s="74"/>
       <c r="H35" s="74"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="74"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="72" t="s">
         <v>309</v>
       </c>
@@ -6557,6 +6566,7 @@
       </c>
       <c r="G36" s="74"/>
       <c r="H36" s="74"/>
+      <c r="I36" s="74"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="72" t="s">
@@ -6569,7 +6579,7 @@
       <c r="E38" s="27"/>
       <c r="F38" s="27"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="75" t="s">
         <v>129</v>
       </c>
@@ -6579,29 +6589,30 @@
       <c r="F40" s="75"/>
       <c r="G40" s="75"/>
       <c r="H40" s="75"/>
+      <c r="I40" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Formula_Export_Microschool_With_Decisions.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Microschool_With_Decisions.xlsx
@@ -38,7 +38,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated May 7, 2026 · llc_single</t>
+    <t>Generated May 9, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -785,7 +785,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
